--- a/Resources/SleepyPsycastEffects.xlsx
+++ b/Resources/SleepyPsycastEffects.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="211">
   <si>
     <t>N/A</t>
   </si>
@@ -394,10 +394,6 @@
     <t>Heals scars by 0.2 points every 10 seconds (Approx total of 6.0 points)</t>
   </si>
   <si>
-    <t>Repairs item by this formula:
-((MaxHitPoints - CurrentHitPoints) / 2 ) + (MaxHitPoints / 20))</t>
-  </si>
-  <si>
     <t>Create a flame explosion at target location</t>
   </si>
   <si>
@@ -618,9 +614,6 @@
     <t>Targets Animals</t>
   </si>
   <si>
-    <t>Force Job Driver of Target Pawn to 'Flee And Cower'</t>
-  </si>
-  <si>
     <t>Spawn Firefoam at Target Location within Effect Range</t>
   </si>
   <si>
@@ -749,9 +742,6 @@
   </si>
   <si>
     <t xml:space="preserve">Phantom Turret  </t>
-  </si>
-  <si>
-    <t>Spawn a temporary ethereal turret to will defend the casters faction. It has low ammo and low health but fires quickly.</t>
   </si>
   <si>
     <t>Clean Stride</t>
@@ -906,6 +896,29 @@
     <t xml:space="preserve">Remove Food Posioning from all stacks of food in target area.
 Remove Metal Horror spores from  all stacks of food in target area.   </t>
   </si>
+  <si>
+    <t>Repairs item by this formula:
+((MaxHitPoints - CurrentHitPoints) / 2 ) + (MaxHitPoints / 20))
+Cannot go over max health of item</t>
+  </si>
+  <si>
+    <t>Bitskip</t>
+  </si>
+  <si>
+    <t>Teleports all items in area of effect (4.9 Tiles) to Target Location.</t>
+  </si>
+  <si>
+    <t>Force Mental State "Terror"</t>
+  </si>
+  <si>
+    <t>Spawn a temporary ethereal turret to defend the casters faction. It has low ammo and low health but fires quickly.</t>
+  </si>
+  <si>
+    <t>Reinforce</t>
+  </si>
+  <si>
+    <t>Increase item or building max health by 20%</t>
+  </si>
 </sst>
 </file>
 
@@ -973,18 +986,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -999,7 +1006,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1120,16 +1127,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1138,20 +1139,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1716,7 +1708,7 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D3" t="s">
         <v>4</v>
@@ -1758,7 +1750,7 @@
         <v>31</v>
       </c>
       <c r="R3" s="13" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="2:18" ht="30">
@@ -1766,13 +1758,13 @@
         <v>12</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F4" s="6">
         <v>1</v>
@@ -1810,16 +1802,16 @@
     </row>
     <row r="5" spans="2:18" s="2" customFormat="1" ht="45">
       <c r="B5" s="17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
@@ -1846,7 +1838,7 @@
         <v>-1</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O5" s="6" t="s">
         <v>0</v>
@@ -1860,7 +1852,7 @@
         <v>89</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>18</v>
@@ -1907,7 +1899,7 @@
         <v>48</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>18</v>
@@ -1928,7 +1920,7 @@
         <v>240</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K7" s="16">
         <v>0.1</v>
@@ -1954,13 +1946,13 @@
         <v>49</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F8" s="3">
         <v>1</v>
@@ -1998,16 +1990,16 @@
     </row>
     <row r="9" spans="2:18" ht="60">
       <c r="B9" s="26" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D9" s="17" t="s">
         <v>94</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F9" s="6">
         <v>1</v>
@@ -2045,16 +2037,16 @@
     </row>
     <row r="10" spans="2:18" ht="90">
       <c r="B10" s="17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F10" s="20">
         <v>2</v>
@@ -2095,13 +2087,13 @@
         <v>21</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F11" s="3">
         <v>2</v>
@@ -2142,7 +2134,7 @@
         <v>17</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>18</v>
@@ -2189,7 +2181,7 @@
         <v>59</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>18</v>
@@ -2233,16 +2225,16 @@
     </row>
     <row r="14" spans="2:18" ht="30">
       <c r="B14" s="17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F14" s="3">
         <v>2</v>
@@ -2283,7 +2275,7 @@
         <v>53</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>70</v>
@@ -2330,7 +2322,7 @@
         <v>54</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>70</v>
@@ -2377,13 +2369,13 @@
         <v>40</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F17" s="6">
         <v>3</v>
@@ -2421,16 +2413,16 @@
     </row>
     <row r="18" spans="2:16" ht="90">
       <c r="B18" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C18" s="27" t="s">
-        <v>138</v>
-      </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="F18" s="6">
         <v>3</v>
@@ -2471,7 +2463,7 @@
         <v>57</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>18</v>
@@ -2515,16 +2507,16 @@
     </row>
     <row r="20" spans="2:16" ht="30">
       <c r="B20" s="17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F20" s="6">
         <v>3</v>
@@ -2539,7 +2531,7 @@
         <v>30000</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K20" s="16">
         <v>0.2</v>
@@ -2565,13 +2557,13 @@
         <v>93</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D21" s="17" t="s">
         <v>94</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F21" s="6">
         <v>3</v>
@@ -2612,13 +2604,13 @@
         <v>33</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F22" s="6">
         <v>3</v>
@@ -2633,7 +2625,7 @@
         <v>84</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K22" s="16">
         <v>0.5</v>
@@ -2648,10 +2640,10 @@
         <v>26</v>
       </c>
       <c r="O22" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="P22" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="23" spans="2:16">
@@ -2659,7 +2651,7 @@
         <v>63</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>65</v>
@@ -2706,7 +2698,7 @@
         <v>61</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>23</v>
@@ -2753,7 +2745,7 @@
         <v>62</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>23</v>
@@ -2800,7 +2792,7 @@
         <v>36</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>34</v>
@@ -2839,21 +2831,21 @@
         <v>35</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="2:16" ht="45">
       <c r="B27" s="17" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F27" s="6">
         <v>3</v>
@@ -2868,7 +2860,7 @@
         <v>10000</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K27" s="16">
         <v>0.2</v>
@@ -2894,7 +2886,7 @@
         <v>58</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>18</v>
@@ -2941,7 +2933,7 @@
         <v>22</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D29" s="17" t="s">
         <v>24</v>
@@ -2977,24 +2969,24 @@
         <v>26</v>
       </c>
       <c r="O29" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="P29" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="30" spans="2:16" ht="30">
       <c r="B30" s="17" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C30" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>70</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F30" s="6">
         <v>4</v>
@@ -3021,7 +3013,7 @@
         <v>-1</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O30" s="6"/>
       <c r="P30" s="6"/>
@@ -3031,7 +3023,7 @@
         <v>66</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>65</v>
@@ -3078,7 +3070,7 @@
         <v>55</v>
       </c>
       <c r="C32" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>14</v>
@@ -3099,7 +3091,7 @@
         <v>84</v>
       </c>
       <c r="J32" s="16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K32" s="16">
         <v>1</v>
@@ -3125,7 +3117,7 @@
         <v>64</v>
       </c>
       <c r="C33" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>65</v>
@@ -3172,7 +3164,7 @@
         <v>60</v>
       </c>
       <c r="C34" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>23</v>
@@ -3219,13 +3211,13 @@
         <v>56</v>
       </c>
       <c r="C35" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F35" s="6">
         <v>5</v>
@@ -3240,7 +3232,7 @@
         <v>500</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K35" s="16">
         <v>3</v>
@@ -3255,24 +3247,24 @@
         <v>26</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="36" spans="2:16" ht="45">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="36" spans="2:16" ht="60">
       <c r="B36" s="17" t="s">
         <v>51</v>
       </c>
       <c r="C36" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>96</v>
+        <v>204</v>
       </c>
       <c r="F36" s="3">
         <v>5</v>
@@ -3310,16 +3302,16 @@
     </row>
     <row r="37" spans="2:16" ht="45">
       <c r="B37" s="17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C37" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F37" s="6">
         <v>5</v>
@@ -3334,7 +3326,7 @@
         <v>10000</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K37" s="16">
         <v>5</v>
@@ -3349,10 +3341,10 @@
         <v>26</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="2:16" ht="60">
@@ -3360,7 +3352,7 @@
         <v>46</v>
       </c>
       <c r="C38" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>23</v>
@@ -3407,7 +3399,7 @@
         <v>38</v>
       </c>
       <c r="C39" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D39" s="17" t="s">
         <v>41</v>
@@ -3451,16 +3443,16 @@
     </row>
     <row r="40" spans="2:16" ht="45">
       <c r="B40" s="17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C40" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F40" s="6">
         <v>6</v>
@@ -3493,17 +3485,17 @@
       <c r="P40" s="6"/>
     </row>
     <row r="41" spans="2:16" ht="45">
-      <c r="B41" s="44" t="s">
-        <v>192</v>
+      <c r="B41" s="43" t="s">
+        <v>189</v>
       </c>
       <c r="C41" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F41" s="6">
         <v>2</v>
@@ -3537,16 +3529,16 @@
     </row>
     <row r="42" spans="2:16" ht="30">
       <c r="B42" s="17" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C42" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D42" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E42" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>157</v>
       </c>
       <c r="F42" s="6">
         <v>2</v>
@@ -3561,7 +3553,7 @@
         <v>504</v>
       </c>
       <c r="J42" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K42" s="16">
         <v>1</v>
@@ -3573,7 +3565,7 @@
         <v>39.9</v>
       </c>
       <c r="N42" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O42" s="8" t="s">
         <v>0</v>
@@ -3584,16 +3576,16 @@
     </row>
     <row r="43" spans="2:16" ht="30">
       <c r="B43" s="29" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C43" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>18</v>
       </c>
       <c r="E43" s="30" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F43" s="6">
         <v>2</v>
@@ -3620,7 +3612,7 @@
         <v>-1</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="O43" s="8" t="s">
         <v>0</v>
@@ -3631,16 +3623,16 @@
     </row>
     <row r="44" spans="2:16" ht="150">
       <c r="B44" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C44" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F44" s="2">
         <v>3</v>
@@ -3655,7 +3647,7 @@
         <v>1512</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="K44" s="38">
         <v>3.5</v>
@@ -3667,7 +3659,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="O44" s="39"/>
       <c r="P44" s="8" t="s">
@@ -3676,16 +3668,16 @@
     </row>
     <row r="45" spans="2:16" ht="45">
       <c r="B45" s="17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C45" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>18</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F45" s="6">
         <v>3</v>
@@ -3723,16 +3715,16 @@
     </row>
     <row r="46" spans="2:16" ht="30">
       <c r="B46" s="17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C46" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E46" s="36" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F46" s="6">
         <v>4</v>
@@ -3770,16 +3762,16 @@
     </row>
     <row r="47" spans="2:16" ht="30">
       <c r="B47" s="17" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C47" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F47" s="6">
         <v>4</v>
@@ -3817,16 +3809,16 @@
     </row>
     <row r="48" spans="2:16" ht="30">
       <c r="B48" s="17" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C48" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F48" s="6">
         <v>4</v>
@@ -3864,16 +3856,16 @@
     </row>
     <row r="49" spans="2:16" ht="45">
       <c r="B49" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="C49" s="34" t="s">
         <v>146</v>
-      </c>
-      <c r="C49" s="34" t="s">
-        <v>147</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F49" s="6">
         <v>6</v>
@@ -3888,7 +3880,7 @@
         <v>4032</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K49" s="16">
         <v>1</v>
@@ -3911,16 +3903,16 @@
     </row>
     <row r="50" spans="2:16" ht="45">
       <c r="B50" s="17" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C50" s="35" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E50" s="36" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F50" s="6">
         <v>1</v>
@@ -3935,7 +3927,7 @@
         <v>252</v>
       </c>
       <c r="J50" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="K50" s="32">
         <v>0.5</v>
@@ -3958,16 +3950,16 @@
     </row>
     <row r="51" spans="2:16" ht="45">
       <c r="B51" s="17" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C51" s="35" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F51" s="6">
         <v>2</v>
@@ -3982,7 +3974,7 @@
         <v>180</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="K51" s="16">
         <v>1.5</v>
@@ -4005,16 +3997,16 @@
     </row>
     <row r="52" spans="2:16" ht="45">
       <c r="B52" s="40" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C52" s="35" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D52" s="40" t="s">
         <v>18</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F52" s="6">
         <v>2</v>
@@ -4050,18 +4042,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:16" ht="90">
-      <c r="B53" s="44" t="s">
-        <v>194</v>
+    <row r="53" spans="2:16" s="2" customFormat="1" ht="90">
+      <c r="B53" s="43" t="s">
+        <v>191</v>
       </c>
       <c r="C53" s="35" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F53" s="6">
         <v>2</v>
@@ -4090,21 +4082,19 @@
       <c r="N53" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="O53" s="2"/>
-      <c r="P53" s="2"/>
     </row>
     <row r="54" spans="2:16" ht="45">
       <c r="B54" s="40" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C54" s="35" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D54" s="40" t="s">
         <v>18</v>
       </c>
       <c r="E54" s="36" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F54" s="6">
         <v>3</v>
@@ -4140,18 +4130,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:16" s="2" customFormat="1" ht="45">
+    <row r="55" spans="2:16" ht="45">
       <c r="B55" s="40" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C55" s="35" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D55" s="40" t="s">
         <v>18</v>
       </c>
       <c r="E55" s="36" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F55" s="6">
         <v>3</v>
@@ -4180,19 +4170,21 @@
       <c r="N55" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="O55" s="2"/>
+      <c r="P55" s="2"/>
     </row>
     <row r="56" spans="2:16" ht="30">
       <c r="B56" s="29" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C56" s="35" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E56" s="37" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F56" s="6">
         <v>3</v>
@@ -4207,7 +4199,7 @@
         <v>252</v>
       </c>
       <c r="J56" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="K56" s="32">
         <v>1</v>
@@ -4230,16 +4222,16 @@
     </row>
     <row r="57" spans="2:16" ht="45">
       <c r="B57" s="17" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C57" s="35" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E57" s="36" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F57" s="6">
         <v>4</v>
@@ -4254,7 +4246,7 @@
         <v>252</v>
       </c>
       <c r="J57" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="K57" s="32">
         <v>0.5</v>
@@ -4277,16 +4269,16 @@
     </row>
     <row r="58" spans="2:16" ht="90">
       <c r="B58" s="41" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C58" s="35" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F58" s="6">
         <v>4</v>
@@ -4301,7 +4293,7 @@
         <v>336</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K58" s="16">
         <v>3</v>
@@ -4316,24 +4308,24 @@
         <v>26</v>
       </c>
       <c r="O58" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P58" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="59" spans="2:16" ht="30">
       <c r="B59" s="17" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C59" s="35" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D59" s="17" t="s">
         <v>18</v>
       </c>
       <c r="E59" s="36" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F59" s="6">
         <v>5</v>
@@ -4348,7 +4340,7 @@
         <v>25</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="K59" s="16">
         <v>0.1</v>
@@ -4370,17 +4362,17 @@
       </c>
     </row>
     <row r="60" spans="2:16" ht="60">
-      <c r="B60" s="43" t="s">
-        <v>187</v>
+      <c r="B60" s="42" t="s">
+        <v>185</v>
       </c>
       <c r="C60" s="35" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E60" s="37" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F60" s="2">
         <v>5</v>
@@ -4395,7 +4387,7 @@
         <v>252</v>
       </c>
       <c r="J60" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="K60" s="16">
         <v>1</v>
@@ -4418,16 +4410,16 @@
     </row>
     <row r="61" spans="2:16" ht="60">
       <c r="B61" s="17" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C61" s="35" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D61" s="17" t="s">
         <v>94</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F61" s="6">
         <v>6</v>
@@ -4670,7 +4662,7 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D3" t="s">
         <v>4</v>
@@ -4713,17 +4705,17 @@
       </c>
     </row>
     <row r="4" spans="2:16" ht="45">
-      <c r="B4" s="17" t="s">
-        <v>141</v>
+      <c r="B4" s="43" t="s">
+        <v>140</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>150</v>
+        <v>207</v>
       </c>
       <c r="F4" s="6">
         <v>3</v>
@@ -4757,16 +4749,16 @@
     </row>
     <row r="5" spans="2:16" s="2" customFormat="1" ht="30">
       <c r="B5" s="17" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>94</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F5" s="6">
         <v>4</v>
@@ -4800,16 +4792,16 @@
     </row>
     <row r="6" spans="2:16" ht="30">
       <c r="B6" s="17" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>94</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F6" s="6">
         <v>3</v>
@@ -4843,16 +4835,16 @@
     </row>
     <row r="7" spans="2:16" ht="45">
       <c r="B7" s="17" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F7" s="6">
         <v>6</v>
@@ -4885,17 +4877,17 @@
       <c r="P7" s="6"/>
     </row>
     <row r="8" spans="2:16" ht="60">
-      <c r="B8" s="44" t="s">
-        <v>190</v>
+      <c r="B8" s="43" t="s">
+        <v>188</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="F8" s="6">
         <v>6</v>
@@ -4910,7 +4902,7 @@
         <v>84</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K8" s="16">
         <v>0.5</v>
@@ -4928,17 +4920,17 @@
       <c r="P8" s="8"/>
     </row>
     <row r="9" spans="2:16" ht="60">
-      <c r="B9" s="42" t="s">
-        <v>188</v>
+      <c r="B9" s="47" t="s">
+        <v>186</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F9" s="6">
         <v>1</v>
@@ -4958,38 +4950,111 @@
       <c r="K9" s="16">
         <v>1</v>
       </c>
-      <c r="L9" s="14" t="s">
-        <v>0</v>
+      <c r="L9" s="14">
+        <v>3.9</v>
       </c>
       <c r="M9" s="16">
-        <v>-1</v>
+        <v>5.9</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="O9" s="6"/>
       <c r="P9" s="6"/>
     </row>
-    <row r="10" spans="2:16">
-      <c r="O10" s="8"/>
-      <c r="P10" s="8"/>
-    </row>
-    <row r="11" spans="2:16">
-      <c r="B11" s="44"/>
-      <c r="C11" s="45"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="47"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="49"/>
-      <c r="I11" s="50"/>
-      <c r="J11" s="47"/>
-      <c r="K11" s="51"/>
-      <c r="L11" s="52"/>
-      <c r="M11" s="51"/>
-      <c r="N11" s="46"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
+    <row r="10" spans="2:16" ht="45">
+      <c r="B10" s="43" t="s">
+        <v>205</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="F10" s="3">
+        <v>3</v>
+      </c>
+      <c r="G10" s="5">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="H10" s="4">
+        <v>25</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="K10" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="L10" s="14">
+        <v>49.9</v>
+      </c>
+      <c r="M10" s="16">
+        <v>5.9</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="O10" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="P10" s="46" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" ht="30">
+      <c r="B11" s="43" t="s">
+        <v>209</v>
+      </c>
+      <c r="C11" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="44" t="s">
+        <v>210</v>
+      </c>
+      <c r="F11" s="45">
+        <v>6</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="H11" s="4">
+        <v>60</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="K11" s="16">
+        <v>1.5</v>
+      </c>
+      <c r="L11" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="M11" s="16">
+        <v>-1</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="O11" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="P11" s="6" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="2:16">
       <c r="B12" s="17"/>

--- a/Resources/SleepyPsycastEffects.xlsx
+++ b/Resources/SleepyPsycastEffects.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="27735" windowHeight="10755" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="27735" windowHeight="10755"/>
   </bookViews>
   <sheets>
     <sheet name="SLP More Psycasts" sheetId="1" r:id="rId1"/>
@@ -162,10 +162,6 @@
   </si>
   <si>
     <t>Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0 Days - Phoenix Syndrome
-RNG: 1.5 to 2.5 Days -Resurrection Sickness </t>
   </si>
   <si>
     <r>
@@ -918,6 +914,10 @@
   </si>
   <si>
     <t>Increase item or building max health by 20%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0 Days - Phoenix Syndrome
+RNG: 1.5 to 2.5 Days -Resurrection Sickness </t>
   </si>
 </sst>
 </file>
@@ -1708,7 +1708,7 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D3" t="s">
         <v>4</v>
@@ -1750,7 +1750,7 @@
         <v>31</v>
       </c>
       <c r="R3" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="2:18" ht="30">
@@ -1758,13 +1758,13 @@
         <v>12</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F4" s="6">
         <v>1</v>
@@ -1802,16 +1802,16 @@
     </row>
     <row r="5" spans="2:18" s="2" customFormat="1" ht="45">
       <c r="B5" s="17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
@@ -1838,7 +1838,7 @@
         <v>-1</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O5" s="6" t="s">
         <v>0</v>
@@ -1849,16 +1849,16 @@
     </row>
     <row r="6" spans="2:18" ht="45">
       <c r="B6" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F6" s="3">
         <v>1</v>
@@ -1896,16 +1896,16 @@
     </row>
     <row r="7" spans="2:18" ht="45">
       <c r="B7" s="17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F7" s="3">
         <v>1</v>
@@ -1920,7 +1920,7 @@
         <v>240</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K7" s="16">
         <v>0.1</v>
@@ -1943,16 +1943,16 @@
     </row>
     <row r="8" spans="2:18" ht="30">
       <c r="B8" s="17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F8" s="3">
         <v>1</v>
@@ -1979,7 +1979,7 @@
         <v>12.9</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>0</v>
@@ -1990,16 +1990,16 @@
     </row>
     <row r="9" spans="2:18" ht="60">
       <c r="B9" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="F9" s="6">
         <v>1</v>
@@ -2026,7 +2026,7 @@
         <v>28.9</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>0</v>
@@ -2037,16 +2037,16 @@
     </row>
     <row r="10" spans="2:18" ht="90">
       <c r="B10" s="17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F10" s="20">
         <v>2</v>
@@ -2073,7 +2073,7 @@
         <v>9.9</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O10" s="20" t="s">
         <v>0</v>
@@ -2087,13 +2087,13 @@
         <v>21</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F11" s="3">
         <v>2</v>
@@ -2134,7 +2134,7 @@
         <v>17</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>18</v>
@@ -2178,16 +2178,16 @@
     </row>
     <row r="13" spans="2:18" ht="30">
       <c r="B13" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F13" s="6">
         <v>2</v>
@@ -2202,7 +2202,7 @@
         <v>3000</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K13" s="16">
         <v>2</v>
@@ -2214,7 +2214,7 @@
         <v>-1</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O13" s="8" t="s">
         <v>0</v>
@@ -2225,16 +2225,16 @@
     </row>
     <row r="14" spans="2:18" ht="30">
       <c r="B14" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F14" s="3">
         <v>2</v>
@@ -2249,7 +2249,7 @@
         <v>8000</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K14" s="16">
         <v>2</v>
@@ -2261,7 +2261,7 @@
         <v>-1</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O14" s="8" t="s">
         <v>0</v>
@@ -2272,16 +2272,16 @@
     </row>
     <row r="15" spans="2:18" ht="45">
       <c r="B15" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F15" s="3">
         <v>2</v>
@@ -2319,16 +2319,16 @@
     </row>
     <row r="16" spans="2:18" ht="45">
       <c r="B16" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F16" s="3">
         <v>2</v>
@@ -2369,13 +2369,13 @@
         <v>40</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F17" s="6">
         <v>3</v>
@@ -2413,16 +2413,16 @@
     </row>
     <row r="18" spans="2:16" ht="90">
       <c r="B18" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C18" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>104</v>
       </c>
       <c r="F18" s="6">
         <v>3</v>
@@ -2460,16 +2460,16 @@
     </row>
     <row r="19" spans="2:16" ht="45">
       <c r="B19" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F19" s="3">
         <v>3</v>
@@ -2484,7 +2484,7 @@
         <v>168</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K19" s="16">
         <v>0.1</v>
@@ -2507,16 +2507,16 @@
     </row>
     <row r="20" spans="2:16" ht="30">
       <c r="B20" s="17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F20" s="6">
         <v>3</v>
@@ -2531,7 +2531,7 @@
         <v>30000</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K20" s="16">
         <v>0.2</v>
@@ -2554,16 +2554,16 @@
     </row>
     <row r="21" spans="2:16" ht="60">
       <c r="B21" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="D21" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="C21" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>94</v>
-      </c>
       <c r="E21" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F21" s="6">
         <v>3</v>
@@ -2590,7 +2590,7 @@
         <v>19.899999999999999</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>0</v>
@@ -2604,13 +2604,13 @@
         <v>33</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F22" s="6">
         <v>3</v>
@@ -2625,7 +2625,7 @@
         <v>84</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K22" s="16">
         <v>0.5</v>
@@ -2640,24 +2640,24 @@
         <v>26</v>
       </c>
       <c r="O22" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="P22" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="23" spans="2:16">
       <c r="B23" s="17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F23" s="3">
         <v>3</v>
@@ -2684,7 +2684,7 @@
         <v>22.9</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O23" s="8" t="s">
         <v>0</v>
@@ -2695,16 +2695,16 @@
     </row>
     <row r="24" spans="2:16" ht="60">
       <c r="B24" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F24" s="3">
         <v>3</v>
@@ -2719,7 +2719,7 @@
         <v>20</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K24" s="8">
         <v>0.25</v>
@@ -2731,7 +2731,7 @@
         <v>24.9</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O24" s="8" t="s">
         <v>0</v>
@@ -2742,16 +2742,16 @@
     </row>
     <row r="25" spans="2:16" ht="60">
       <c r="B25" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F25" s="3">
         <v>3</v>
@@ -2766,7 +2766,7 @@
         <v>3</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K25" s="8">
         <v>0.25</v>
@@ -2778,7 +2778,7 @@
         <v>20.9</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O25" s="8" t="s">
         <v>0</v>
@@ -2792,13 +2792,13 @@
         <v>36</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F26" s="6">
         <v>3</v>
@@ -2831,21 +2831,21 @@
         <v>35</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="2:16" ht="45">
       <c r="B27" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F27" s="6">
         <v>3</v>
@@ -2860,7 +2860,7 @@
         <v>10000</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K27" s="16">
         <v>0.2</v>
@@ -2883,16 +2883,16 @@
     </row>
     <row r="28" spans="2:16" ht="30">
       <c r="B28" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F28" s="3">
         <v>3</v>
@@ -2907,7 +2907,7 @@
         <v>8000</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K28" s="16">
         <v>2</v>
@@ -2919,7 +2919,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O28" s="8" t="s">
         <v>0</v>
@@ -2933,7 +2933,7 @@
         <v>22</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D29" s="17" t="s">
         <v>24</v>
@@ -2969,24 +2969,24 @@
         <v>26</v>
       </c>
       <c r="O29" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="P29" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="30" spans="2:16" ht="30">
       <c r="B30" s="17" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C30" s="27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F30" s="6">
         <v>4</v>
@@ -3013,32 +3013,32 @@
         <v>-1</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O30" s="6"/>
       <c r="P30" s="6"/>
     </row>
     <row r="31" spans="2:16" ht="30">
       <c r="B31" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="C31" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="C31" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="F31" s="6">
         <v>4</v>
       </c>
       <c r="G31" s="5">
-        <v>1.4999999999999999E-2</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="H31" s="4">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I31" s="8" t="s">
         <v>0</v>
@@ -3053,10 +3053,10 @@
         <v>0</v>
       </c>
       <c r="M31" s="16">
-        <v>32.9</v>
+        <v>33.9</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O31" s="6" t="s">
         <v>0</v>
@@ -3067,16 +3067,16 @@
     </row>
     <row r="32" spans="2:16" ht="60">
       <c r="B32" s="17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C32" s="27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F32" s="6">
         <v>4</v>
@@ -3091,7 +3091,7 @@
         <v>84</v>
       </c>
       <c r="J32" s="16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K32" s="16">
         <v>1</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="33" spans="2:16">
       <c r="B33" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C33" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="E33" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F33" s="3">
         <v>4</v>
@@ -3150,7 +3150,7 @@
         <v>31.9</v>
       </c>
       <c r="N33" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O33" s="8" t="s">
         <v>0</v>
@@ -3161,16 +3161,16 @@
     </row>
     <row r="34" spans="2:16" ht="60">
       <c r="B34" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C34" s="27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F34" s="3">
         <v>5</v>
@@ -3185,7 +3185,7 @@
         <v>8</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K34" s="8">
         <v>0.25</v>
@@ -3197,7 +3197,7 @@
         <v>18.899999999999999</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O34" s="8" t="s">
         <v>0</v>
@@ -3208,16 +3208,16 @@
     </row>
     <row r="35" spans="2:16" ht="150">
       <c r="B35" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C35" s="27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F35" s="6">
         <v>5</v>
@@ -3232,7 +3232,7 @@
         <v>500</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K35" s="16">
         <v>3</v>
@@ -3247,24 +3247,24 @@
         <v>26</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="60">
       <c r="B36" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C36" s="27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F36" s="3">
         <v>5</v>
@@ -3291,7 +3291,7 @@
         <v>14.9</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>0</v>
@@ -3302,16 +3302,16 @@
     </row>
     <row r="37" spans="2:16" ht="45">
       <c r="B37" s="17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C37" s="27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F37" s="6">
         <v>5</v>
@@ -3326,7 +3326,7 @@
         <v>10000</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K37" s="16">
         <v>5</v>
@@ -3341,24 +3341,24 @@
         <v>26</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="2:16" ht="60">
       <c r="B38" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C38" s="27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F38" s="3">
         <v>6</v>
@@ -3399,7 +3399,7 @@
         <v>38</v>
       </c>
       <c r="C39" s="27" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D39" s="17" t="s">
         <v>41</v>
@@ -3432,27 +3432,27 @@
         <v>-1</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>43</v>
+        <v>210</v>
       </c>
     </row>
     <row r="40" spans="2:16" ht="45">
       <c r="B40" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="C40" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E40" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="C40" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>129</v>
       </c>
       <c r="F40" s="6">
         <v>6</v>
@@ -3486,16 +3486,16 @@
     </row>
     <row r="41" spans="2:16" ht="45">
       <c r="B41" s="43" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C41" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F41" s="6">
         <v>2</v>
@@ -3510,7 +3510,7 @@
         <v>3024</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K41" s="16">
         <v>1</v>
@@ -3529,16 +3529,16 @@
     </row>
     <row r="42" spans="2:16" ht="30">
       <c r="B42" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="C42" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E42" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="C42" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>155</v>
       </c>
       <c r="F42" s="6">
         <v>2</v>
@@ -3553,7 +3553,7 @@
         <v>504</v>
       </c>
       <c r="J42" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K42" s="16">
         <v>1</v>
@@ -3565,7 +3565,7 @@
         <v>39.9</v>
       </c>
       <c r="N42" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O42" s="8" t="s">
         <v>0</v>
@@ -3576,16 +3576,16 @@
     </row>
     <row r="43" spans="2:16" ht="30">
       <c r="B43" s="29" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C43" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>18</v>
       </c>
       <c r="E43" s="30" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F43" s="6">
         <v>2</v>
@@ -3600,7 +3600,7 @@
         <v>3024</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K43" s="32">
         <v>2</v>
@@ -3612,7 +3612,7 @@
         <v>-1</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="O43" s="8" t="s">
         <v>0</v>
@@ -3623,16 +3623,16 @@
     </row>
     <row r="44" spans="2:16" ht="150">
       <c r="B44" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C44" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F44" s="2">
         <v>3</v>
@@ -3647,7 +3647,7 @@
         <v>1512</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K44" s="38">
         <v>3.5</v>
@@ -3659,7 +3659,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="O44" s="39"/>
       <c r="P44" s="8" t="s">
@@ -3668,16 +3668,16 @@
     </row>
     <row r="45" spans="2:16" ht="45">
       <c r="B45" s="17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C45" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>18</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F45" s="6">
         <v>3</v>
@@ -3704,7 +3704,7 @@
         <v>-1</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O45" s="8" t="s">
         <v>0</v>
@@ -3715,16 +3715,16 @@
     </row>
     <row r="46" spans="2:16" ht="30">
       <c r="B46" s="17" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C46" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E46" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F46" s="6">
         <v>4</v>
@@ -3739,7 +3739,7 @@
         <v>15</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K46" s="16">
         <v>0.5</v>
@@ -3751,7 +3751,7 @@
         <v>30.9</v>
       </c>
       <c r="N46" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O46" s="8" t="s">
         <v>0</v>
@@ -3762,16 +3762,16 @@
     </row>
     <row r="47" spans="2:16" ht="30">
       <c r="B47" s="17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C47" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F47" s="6">
         <v>4</v>
@@ -3809,16 +3809,16 @@
     </row>
     <row r="48" spans="2:16" ht="30">
       <c r="B48" s="17" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C48" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F48" s="6">
         <v>4</v>
@@ -3856,16 +3856,16 @@
     </row>
     <row r="49" spans="2:16" ht="45">
       <c r="B49" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="C49" s="34" t="s">
         <v>145</v>
-      </c>
-      <c r="C49" s="34" t="s">
-        <v>146</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F49" s="6">
         <v>6</v>
@@ -3880,7 +3880,7 @@
         <v>4032</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K49" s="16">
         <v>1</v>
@@ -3903,16 +3903,16 @@
     </row>
     <row r="50" spans="2:16" ht="45">
       <c r="B50" s="17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C50" s="35" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E50" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F50" s="6">
         <v>1</v>
@@ -3927,7 +3927,7 @@
         <v>252</v>
       </c>
       <c r="J50" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K50" s="32">
         <v>0.5</v>
@@ -3950,16 +3950,16 @@
     </row>
     <row r="51" spans="2:16" ht="45">
       <c r="B51" s="17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C51" s="35" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F51" s="6">
         <v>2</v>
@@ -3974,7 +3974,7 @@
         <v>180</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K51" s="16">
         <v>1.5</v>
@@ -3997,16 +3997,16 @@
     </row>
     <row r="52" spans="2:16" ht="45">
       <c r="B52" s="40" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C52" s="35" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D52" s="40" t="s">
         <v>18</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F52" s="6">
         <v>2</v>
@@ -4021,7 +4021,7 @@
         <v>168</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K52" s="16">
         <v>1</v>
@@ -4044,16 +4044,16 @@
     </row>
     <row r="53" spans="2:16" s="2" customFormat="1" ht="90">
       <c r="B53" s="43" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C53" s="35" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F53" s="6">
         <v>2</v>
@@ -4068,7 +4068,7 @@
         <v>168</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K53" s="16">
         <v>1</v>
@@ -4080,21 +4080,21 @@
         <v>-1</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="54" spans="2:16" ht="45">
       <c r="B54" s="40" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C54" s="35" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D54" s="40" t="s">
         <v>18</v>
       </c>
       <c r="E54" s="36" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F54" s="6">
         <v>3</v>
@@ -4132,16 +4132,16 @@
     </row>
     <row r="55" spans="2:16" ht="45">
       <c r="B55" s="40" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C55" s="35" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D55" s="40" t="s">
         <v>18</v>
       </c>
       <c r="E55" s="36" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F55" s="6">
         <v>3</v>
@@ -4175,16 +4175,16 @@
     </row>
     <row r="56" spans="2:16" ht="30">
       <c r="B56" s="29" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C56" s="35" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E56" s="37" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F56" s="6">
         <v>3</v>
@@ -4199,7 +4199,7 @@
         <v>252</v>
       </c>
       <c r="J56" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K56" s="32">
         <v>1</v>
@@ -4211,7 +4211,7 @@
         <v>45.9</v>
       </c>
       <c r="N56" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O56" s="8" t="s">
         <v>0</v>
@@ -4222,16 +4222,16 @@
     </row>
     <row r="57" spans="2:16" ht="45">
       <c r="B57" s="17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C57" s="35" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E57" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F57" s="6">
         <v>4</v>
@@ -4246,7 +4246,7 @@
         <v>252</v>
       </c>
       <c r="J57" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K57" s="32">
         <v>0.5</v>
@@ -4269,16 +4269,16 @@
     </row>
     <row r="58" spans="2:16" ht="90">
       <c r="B58" s="41" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C58" s="35" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F58" s="6">
         <v>4</v>
@@ -4293,7 +4293,7 @@
         <v>336</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K58" s="16">
         <v>3</v>
@@ -4308,24 +4308,24 @@
         <v>26</v>
       </c>
       <c r="O58" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P58" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="59" spans="2:16" ht="30">
       <c r="B59" s="17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C59" s="35" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D59" s="17" t="s">
         <v>18</v>
       </c>
       <c r="E59" s="36" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F59" s="6">
         <v>5</v>
@@ -4340,7 +4340,7 @@
         <v>25</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K59" s="16">
         <v>0.1</v>
@@ -4352,7 +4352,7 @@
         <v>-1</v>
       </c>
       <c r="N59" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O59" s="8" t="s">
         <v>0</v>
@@ -4363,16 +4363,16 @@
     </row>
     <row r="60" spans="2:16" ht="60">
       <c r="B60" s="42" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C60" s="35" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E60" s="37" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F60" s="2">
         <v>5</v>
@@ -4387,7 +4387,7 @@
         <v>252</v>
       </c>
       <c r="J60" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K60" s="16">
         <v>1</v>
@@ -4410,16 +4410,16 @@
     </row>
     <row r="61" spans="2:16" ht="60">
       <c r="B61" s="17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C61" s="35" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F61" s="6">
         <v>6</v>
@@ -4446,7 +4446,7 @@
         <v>24.9</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O61" s="8" t="s">
         <v>0</v>
@@ -4662,7 +4662,7 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D3" t="s">
         <v>4</v>
@@ -4706,16 +4706,16 @@
     </row>
     <row r="4" spans="2:16" ht="45">
       <c r="B4" s="43" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F4" s="6">
         <v>3</v>
@@ -4730,7 +4730,7 @@
         <v>8</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K4" s="8">
         <v>0.25</v>
@@ -4749,16 +4749,16 @@
     </row>
     <row r="5" spans="2:16" s="2" customFormat="1" ht="30">
       <c r="B5" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F5" s="6">
         <v>4</v>
@@ -4785,23 +4785,23 @@
         <v>24.9</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
     </row>
     <row r="6" spans="2:16" ht="30">
       <c r="B6" s="17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F6" s="6">
         <v>3</v>
@@ -4828,23 +4828,23 @@
         <v>19.899999999999999</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O6" s="20"/>
       <c r="P6" s="6"/>
     </row>
     <row r="7" spans="2:16" ht="45">
       <c r="B7" s="17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F7" s="6">
         <v>6</v>
@@ -4878,16 +4878,16 @@
     </row>
     <row r="8" spans="2:16" ht="60">
       <c r="B8" s="43" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F8" s="6">
         <v>6</v>
@@ -4902,7 +4902,7 @@
         <v>84</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K8" s="16">
         <v>0.5</v>
@@ -4921,16 +4921,16 @@
     </row>
     <row r="9" spans="2:16" ht="60">
       <c r="B9" s="47" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F9" s="6">
         <v>1</v>
@@ -4957,23 +4957,23 @@
         <v>5.9</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O9" s="6"/>
       <c r="P9" s="6"/>
     </row>
     <row r="10" spans="2:16" ht="45">
       <c r="B10" s="43" t="s">
+        <v>204</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>205</v>
-      </c>
-      <c r="C10" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>206</v>
       </c>
       <c r="F10" s="3">
         <v>3</v>
@@ -5000,7 +5000,7 @@
         <v>5.9</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O10" s="8" t="s">
         <v>0</v>
@@ -5011,16 +5011,16 @@
     </row>
     <row r="11" spans="2:16" ht="30">
       <c r="B11" s="43" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F11" s="45">
         <v>6</v>
@@ -5047,7 +5047,7 @@
         <v>-1</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>0</v>
